--- a/docs/oc-mensuales/licencia-de-software-de-ofimatica/jul-2026.xlsx
+++ b/docs/oc-mensuales/licencia-de-software-de-ofimatica/jul-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M78"/>
+  <dimension ref="A1:M74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1067,7 +1067,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1499684-41-CM26</t>
+          <t>3598-519-CM26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1087,22 +1087,22 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Enviada a Proveedor</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>65.077.905-3</t>
+          <t>69.091.300-3</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>FUNDACION DE CULTURA DE SAN PEDRO DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE MARCHIGUE</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1122,7 +1122,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>2085.36</v>
+        <v>16041.2</v>
       </c>
     </row>
     <row r="12">
@@ -1189,7 +1189,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1057492-2513-CM26</t>
+          <t>3616-82-CM26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1209,32 +1209,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61.959.800-8</t>
+          <t>69.041.100-8</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>HOSPITAL ORIENTE DR LUIS TISNE BROUSSE</t>
+          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1244,13 +1244,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>3169.62</v>
+        <v>6238.42</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3616-82-CM26</t>
+          <t>5768-102-CM26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1275,27 +1275,27 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>69.041.100-8</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.232.892-5</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1305,13 +1305,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>6238.42</v>
+        <v>54978</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>5768-102-CM26</t>
+          <t>1368-34-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>75.980.060-5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>CORPORACIÓN DE FOMENTO DE LA PRODUCCIÓN - CORFO</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>76.232.892-5</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1366,13 +1366,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>54978</v>
+        <v>10769.86</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1368-34-CM26</t>
+          <t>5586-2119-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1397,27 +1397,27 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>75.980.060-5</t>
+          <t>87.912.900-1</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>CORPORACIÓN DE FOMENTO DE LA PRODUCCIÓN - CORFO</t>
+          <t>UNIVERSIDAD DE LA FRONTERA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.232.892-5</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>10769.86</v>
+        <v>62229.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>5586-2119-CM26</t>
+          <t>1315526-15-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1458,27 +1458,27 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>87.912.900-1</t>
+          <t>65.086.019-5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA FRONTERA</t>
+          <t>CORPORACION MUNICIPAL DE FOMENTO AL DESARROLLO ECONOMICO Y PRODUCTIVO</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>76.232.892-5</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1488,13 +1488,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>62229.5</v>
+        <v>7692.76</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1315526-15-CM26</t>
+          <t>2790-194-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1514,17 +1514,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>65.086.019-5</t>
+          <t>69.072.600-9</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE FOMENTO AL DESARROLLO ECONOMICO Y PRODUCTIVO</t>
+          <t>I MUNICIPALIDAD DE PAINE</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1534,12 +1534,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>OPTIMIZA SEGURIDAD SPA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.854.651-7</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1549,13 +1549,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>7692.76</v>
+        <v>17942.82</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2790-194-CM26</t>
+          <t>1057492-2513-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.072.600-9</t>
+          <t>61.959.800-8</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PAINE</t>
+          <t>HOSPITAL ORIENTE DR LUIS TISNE BROUSSE</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>OPTIMIZA SEGURIDAD SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>76.854.651-7</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1610,13 +1610,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>17942.82</v>
+        <v>3169.62</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3598-519-CM26</t>
+          <t>2727-551-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1631,37 +1631,37 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>69.091.300-3</t>
+          <t>69.140.500-1</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MARCHIGUE</t>
+          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>92.580.000-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1671,13 +1671,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>16041.2</v>
+        <v>7096.21</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2727-551-CM26</t>
+          <t>2445-2218-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1702,27 +1702,27 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>69.140.500-1</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1732,13 +1732,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>7096.21</v>
+        <v>4860.09</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2445-2218-CM26</t>
+          <t>2378-223-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1763,17 +1763,17 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>69.070.700-4</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>I MUNICIPALIDAD DE LA FLORIDA</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1793,13 +1793,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>4860.09</v>
+        <v>1479.16</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2378-223-CM26</t>
+          <t>307-56-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>69.070.700-4</t>
+          <t>60.919.000-0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA FLORIDA</t>
+          <t>Consejo de Rectores de las Universidades Chilenas</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1854,13 +1854,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>1479.16</v>
+        <v>2113.08</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>307-56-CM26</t>
+          <t>2021-131-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1880,32 +1880,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>60.919.000-0</t>
+          <t>61.101.040-0</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Consejo de Rectores de las Universidades Chilenas</t>
+          <t>Estado Mayor Conjunto</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1915,13 +1915,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>2113.08</v>
+        <v>21044.51</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2021-131-CM26</t>
+          <t>798018-61-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,32 +1941,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>61.101.040-0</t>
+          <t>65.073.222-7</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Estado Mayor Conjunto</t>
+          <t>DIRECCION DE COMUNICACIONES DE LA ARMADA</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1976,13 +1976,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>21044.51</v>
+        <v>5077.22</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>798018-61-CM26</t>
+          <t>1609-221-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2002,32 +2002,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>65.073.222-7</t>
+          <t>72.229.800-4</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>DIRECCION DE COMUNICACIONES DE LA ARMADA</t>
+          <t>GOBIERNO REGIONAL XII REGION MAGALLANES Y ANTARTICA CHILENA</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Magallanes y Antártica</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2037,13 +2037,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>5077.22</v>
+        <v>12405.21</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1609-221-CM26</t>
+          <t>1609-220-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2083,12 +2083,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2098,13 +2098,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>12405.21</v>
+        <v>64452.54</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1609-220-CM26</t>
+          <t>1417902-21-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2129,17 +2129,17 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>72.229.800-4</t>
+          <t>65.211.127-0</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL XII REGION MAGALLANES Y ANTARTICA CHILENA</t>
+          <t>ASOCIACION DE MUNICIPALIDADES DE LA ZONA METROPOLITANA DE LA ARAUCANIA</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2159,13 +2159,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>64452.54</v>
+        <v>2165.01</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1417902-21-CM26</t>
+          <t>2674-576-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2185,17 +2185,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>65.211.127-0</t>
+          <t>69.072.900-8</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>ASOCIACION DE MUNICIPALIDADES DE LA ZONA METROPOLITANA DE LA ARAUCANIA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE MELIPILLA</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2205,12 +2205,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2220,13 +2220,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>2165.01</v>
+        <v>4226.17</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2674-576-CM26</t>
+          <t>975-207-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2246,17 +2246,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>69.072.900-8</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE MELIPILLA</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2281,13 +2281,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>4226.17</v>
+        <v>1375.54</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>975-207-CM26</t>
+          <t>4077-104-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2302,37 +2302,37 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.979.360-9</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>V ZONA CARABINEROS VALPARAISO</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2342,13 +2342,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>1375.54</v>
+        <v>6761.87</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>4077-104-CM26</t>
+          <t>2424-859-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2368,17 +2368,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.979.360-9</t>
+          <t>69.061.000-0</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>V ZONA CARABINEROS VALPARAISO</t>
+          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2388,12 +2388,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2403,13 +2403,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>6761.87</v>
+        <v>887.03</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2424-859-CM26</t>
+          <t>699360-38-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2434,27 +2434,27 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>69.061.000-0</t>
+          <t>60.505.000-k</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
+          <t>Dirección General de Carabineros de Chile</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2464,13 +2464,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>887.03</v>
+        <v>4587.2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>699360-38-CM26</t>
+          <t>3659-566-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2495,27 +2495,27 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>60.505.000-k</t>
+          <t>69.266.500-7</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>Ilustre Municipalidad de Chillan Viejo</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2525,13 +2525,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>4587.2</v>
+        <v>1031.66</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>3659-566-CM26</t>
+          <t>1057898-83-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2551,17 +2551,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>69.266.500-7</t>
+          <t>61.607.000-2</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Chillan Viejo</t>
+          <t>SERVICIO DE SALUD NUBLE</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2586,13 +2586,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>1031.66</v>
+        <v>15212.96</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1057898-83-CM26</t>
+          <t>539119-2289-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2617,27 +2617,27 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>61.607.000-2</t>
+          <t>60.505.720-9</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD NUBLE</t>
+          <t>Carabineros de Chile - Dirección de Bienestar</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2647,13 +2647,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>15212.96</v>
+        <v>845.23</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1561-110-CM26</t>
+          <t>3517-103-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2668,37 +2668,37 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Enviada a Proveedor</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>61.504.000-2</t>
+          <t>69.180.700-2</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DEL CREDITO PRENDARIO</t>
+          <t>I MUNICIPALIDAD DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>MSLI Latam Inc.</t>
+          <t>CLOUDLATAM SPA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>880443249</t>
+          <t>76.981.642-9</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2708,13 +2708,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>11195.52</v>
+        <v>1774.05</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>539119-2289-CM26</t>
+          <t>858-254-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2729,22 +2729,22 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>60.505.720-9</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2769,13 +2769,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>845.23</v>
+        <v>4470.52</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>858-254-CM26</t>
+          <t>3442-276-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>69.100.700-6</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE VICHUQUEN</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2830,13 +2830,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>4470.52</v>
+        <v>26610.78</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>3517-103-CM26</t>
+          <t>3693-113-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2861,27 +2861,27 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>69.180.700-2</t>
+          <t>69.061.700-5</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TRAIGUEN</t>
+          <t>I MUNICIPALIDAD DE EL QUISCO</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>Site Chile Sociedad Anónima</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
+          <t>96.988.790-8</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>1774.05</v>
+        <v>11602.5</v>
       </c>
     </row>
     <row r="41">
@@ -2958,7 +2958,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1561-109-CM26</t>
+          <t>3573-50-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2973,53 +2973,57 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Enviada a Proveedor</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>61.504.000-2</t>
+          <t>69.201.200-3</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DEL CREDITO PRENDARIO</t>
+          <t>I MUNICIPALIDAD DE PANGUIPULLI</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>MSLI Latam Inc.</t>
+          <t>CLOUDLATAM SPA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>880443249</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
+          <t>76.981.642-9</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>142889.964</v>
+        <v>36123.64</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>3442-276-CM26</t>
+          <t>3073-290-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3034,37 +3038,37 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>69.100.700-6</t>
+          <t>61.102.015-5</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VICHUQUEN</t>
+          <t>SERVICIO HIDROGRAFICO Y OCEANOGRAFICO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3074,13 +3078,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>26610.78</v>
+        <v>5226.19</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>3693-113-CM26</t>
+          <t>2582-255-SE26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3095,7 +3099,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3105,43 +3109,47 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>69.061.700-5</t>
+          <t>69.070.100-6</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE EL QUISCO</t>
+          <t>I MUNICIPALIDAD DE SANTIAGO</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Site Chile Sociedad Anónima</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>96.988.790-8</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>11602.5</v>
+        <v>218562.54</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3573-50-CM26</t>
+          <t>2318-537-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3156,57 +3164,53 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>69.201.200-3</t>
+          <t>69.130.100-1</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PANGUIPULLI</t>
+          <t>I MUNICIPALIDAD DE SAN JAVIER</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>36123.64</v>
+        <v>40280.79</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>3073-290-CM26</t>
+          <t>2360-474-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3221,37 +3225,37 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>61.102.015-5</t>
+          <t>69.150.800-5</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>SERVICIO HIDROGRAFICO Y OCEANOGRAFICO DE LA ARMADA</t>
+          <t>I MUNICIPALIDAD DE TALCAHUANO</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3261,13 +3265,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>5226.19</v>
+        <v>7607.1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2582-255-SE26</t>
+          <t>3420-34-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3282,22 +3286,22 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>69.070.100-6</t>
+          <t>61.101.054-0</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTIAGO</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3307,32 +3311,28 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>218562.54</v>
+        <v>1901.77</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2360-474-CM26</t>
+          <t>836578-87-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3347,7 +3347,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3357,27 +3357,27 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>69.150.800-5</t>
+          <t>61.101.045-1</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCAHUANO</t>
+          <t>Zonas de Bienestar - Jefatura de Zonas</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.334.381-2</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3387,13 +3387,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>7607.1</v>
+        <v>1308.87</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>3420-34-CM26</t>
+          <t>2923-518-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3418,27 +3418,27 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>61.101.054-0</t>
+          <t>69.030.100-8</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>I MUNICIPALIDAD DE CHANARAL</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -3448,13 +3448,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>1901.77</v>
+        <v>10024.98</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1057508-1989-CM26</t>
+          <t>1533460-23-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3469,37 +3469,37 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Enviada a Proveedor</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>61.607.000-2</t>
+          <t>65.261.347-0</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD NUBLE</t>
+          <t>CORPORACIÓN MUNICIPAL DE CULTURA, DEPORTE Y DE FOMENTO DE DESARROLLO C</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3509,13 +3509,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>810.39</v>
+        <v>7130.93</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2318-537-CM26</t>
+          <t>2421-857-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3530,37 +3530,37 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>69.130.100-1</t>
+          <t>69.256.900-8</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN JAVIER</t>
+          <t>Dirección de Administración de Salud Municipal</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>OPTIMIZA SEGURIDAD SPA</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.854.651-7</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -3570,13 +3570,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>40280.79</v>
+        <v>36235.5</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>836578-87-CM26</t>
+          <t>2412-433-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3591,22 +3591,22 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>61.101.045-1</t>
+          <t>69.254.100-6</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Zonas de Bienestar - Jefatura de Zonas</t>
+          <t>I MUNICIPALIDAD DE LO PRADO</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3616,12 +3616,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>76.334.381-2</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -3631,13 +3631,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>1308.87</v>
+        <v>2324.39</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2923-518-CM26</t>
+          <t>1036569-100-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3652,27 +3652,27 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>69.030.100-8</t>
+          <t>62.000.390-5</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHANARAL</t>
+          <t>Gobierno Regional de Ñuble</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3692,13 +3692,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>10024.98</v>
+        <v>32309.57</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1533460-23-CM26</t>
+          <t>2483-477-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>65.261.347-0</t>
+          <t>69.071.300-4</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>CORPORACIÓN MUNICIPAL DE CULTURA, DEPORTE Y DE FOMENTO DE DESARROLLO C</t>
+          <t>I MUNICIPALIDAD DE QUILICURA</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3738,28 +3738,32 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>CLOUDLATAM SPA</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
+          <t>76.981.642-9</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>7130.93</v>
+        <v>175629.72</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2421-857-CM26</t>
+          <t>889473-1191-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3774,37 +3778,37 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>69.256.900-8</t>
+          <t>61.980.530-5</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dirección de Administración de Salud Municipal</t>
+          <t>UNIVERSIDAD DE O'HIGGINS</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>OPTIMIZA SEGURIDAD SPA</t>
+          <t>NETSUS SPA</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>76.854.651-7</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3814,13 +3818,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>36235.5</v>
+        <v>8182.44</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2412-433-CM26</t>
+          <t>1457902-17-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3835,7 +3839,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3845,27 +3849,27 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>69.254.100-6</t>
+          <t>60.501.000-8</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LO PRADO</t>
+          <t xml:space="preserve">Oficina de Seguimiento </t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3875,13 +3879,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>2324.39</v>
+        <v>2641.09</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1036569-100-CM26</t>
+          <t>1068038-18-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3896,7 +3900,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3906,27 +3910,27 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>62.000.390-5</t>
+          <t>60.511.000-2</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Gobierno Regional de Ñuble</t>
+          <t>Pasos Fronterizos</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -3936,13 +3940,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>32309.57</v>
+        <v>1664.43</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2483-477-CM26</t>
+          <t>2343-337-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3957,22 +3961,22 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>69.071.300-4</t>
+          <t>69.070.100-6</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILICURA</t>
+          <t>I MUNICIPALIDAD DE SANTIAGO</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3982,32 +3986,28 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>175629.72</v>
+        <v>4226.17</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>889473-1191-CM26</t>
+          <t>3251-468-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4022,37 +4022,37 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>61.980.530-5</t>
+          <t>69.252.700-3</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE O'HIGGINS</t>
+          <t>I MUNICIPALIDAD DE PELLUHUE</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>NETSUS SPA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -4062,13 +4062,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>8182.44</v>
+        <v>13733.65</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1457902-17-CM26</t>
+          <t>3692-270-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4083,7 +4083,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4093,27 +4093,27 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>60.501.000-8</t>
+          <t>69.061.700-5</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oficina de Seguimiento </t>
+          <t>I MUNICIPALIDAD DE EL QUISCO</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4123,13 +4123,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>2641.09</v>
+        <v>7717.13</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1068038-18-CM26</t>
+          <t>3149-218-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4154,27 +4154,27 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>60.511.000-2</t>
+          <t>69.253.600-2</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pasos Fronterizos</t>
+          <t>I MUNICIPALIDAD DE MARIA ELENA</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.334.381-2</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4184,13 +4184,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>1664.43</v>
+        <v>8436.98</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2343-337-CM26</t>
+          <t>3996-373-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4205,37 +4205,37 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>69.070.100-6</t>
+          <t>69.080.700-9</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTIAGO</t>
+          <t>I MUNICIPALIDAD DE COLTAUCO</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4245,13 +4245,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>4226.17</v>
+        <v>7983.23</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>3251-468-CM26</t>
+          <t>1457282-36-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4276,27 +4276,27 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>69.252.700-3</t>
+          <t>65.011.263-6</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PELLUHUE</t>
+          <t>CORPORACION CENTRO CULTURAL GABRIELA MISTRAL</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -4306,13 +4306,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>13733.65</v>
+        <v>18933.61</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>3692-270-CM26</t>
+          <t>2724-595-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4327,7 +4327,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4337,17 +4337,17 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>69.061.700-5</t>
+          <t>69.140.500-1</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE EL QUISCO</t>
+          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4367,13 +4367,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>7717.13</v>
+        <v>35481.04</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>3149-218-CM26</t>
+          <t>2098-1687-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4388,37 +4388,37 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>69.253.600-2</t>
+          <t>61.602.211-3</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MARIA ELENA</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>76.334.381-2</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -4428,13 +4428,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>8436.98</v>
+        <v>74302.77</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>3996-373-CM26</t>
+          <t>4357-214-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4459,17 +4459,17 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>69.080.700-9</t>
+          <t>69.030.600-k</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COLTAUCO</t>
+          <t>I MUNICIPALIDAD DE FREIRINA</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4489,13 +4489,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>7983.23</v>
+        <v>3846.38</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1457282-36-CM26</t>
+          <t>3420-37-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4510,22 +4510,22 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>65.011.263-6</t>
+          <t>61.101.054-0</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>CORPORACION CENTRO CULTURAL GABRIELA MISTRAL</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4535,12 +4535,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
@@ -4550,13 +4550,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>18933.61</v>
+        <v>21976.06</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2724-595-CM26</t>
+          <t>1602-80-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4571,7 +4571,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4581,27 +4581,27 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>69.140.500-1</t>
+          <t>61.104.000-8</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
@@ -4611,13 +4611,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>35481.04</v>
+        <v>47204.92</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2098-1687-CM26</t>
+          <t>3479-1147-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4632,37 +4632,37 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>61.602.211-3</t>
+          <t>69.220.600-2</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>I MUNICIPALIDAD DE CALBUCO</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
@@ -4672,13 +4672,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>74302.77</v>
+        <v>7923.26</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>4357-214-CM26</t>
+          <t>585-94-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4703,43 +4703,47 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>69.030.600-k</t>
+          <t>82.174.900-k</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FREIRINA</t>
+          <t>SERVICIO DE COOPERACION TECNICA</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>CLOUDLATAM SPA</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr"/>
+          <t>76.981.642-9</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>3846.38</v>
+        <v>326243.38</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>3420-37-CM26</t>
+          <t>514862-462-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4754,22 +4758,22 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>61.101.054-0</t>
+          <t>71.234.100-9</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>CORPORACION MUNICIPAL DE PENALOLEN PARA EL DESARRO</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4779,28 +4783,32 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr"/>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>21976.06</v>
+        <v>21360.5</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1602-80-CM26</t>
+          <t>1195-439-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4815,37 +4823,37 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>69.240.300-2</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
@@ -4855,13 +4863,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>47204.92</v>
+        <v>6062.46</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>3479-1147-CM26</t>
+          <t>4189-468-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4876,7 +4884,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4886,27 +4894,27 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>69.220.600-2</t>
+          <t>69.160.300-8</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALBUCO</t>
+          <t>I MUNICIPALIDAD DE LEBU</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
@@ -4916,13 +4924,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>7923.26</v>
+        <v>15079.44</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>585-94-CM26</t>
+          <t>3731-192-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4937,7 +4945,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4947,288 +4955,36 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>82.174.900-k</t>
+          <t>69.090.300-8</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>SERVICIO DE COOPERACION TECNICA</t>
+          <t>I MUNICIPALIDAD DE CHIMBARONGO</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>NETSUS SPA</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>76.288.338-4</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>326243.379</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>514862-462-CM26</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>2239-11-LR24</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>jul-2026</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>71.234.100-9</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>CORPORACION MUNICIPAL DE PENALOLEN PARA EL DESARRO</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>96.678.350-8</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="n">
-        <v>21360.5</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>1195-439-CM26</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>2239-11-LR24</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>jul-2026</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>69.240.300-2</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Aysén</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>77.700.780-7</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="n">
-        <v>6062.46</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>4189-468-CM26</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>2239-11-LR24</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>jul-2026</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>69.160.300-8</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>I MUNICIPALIDAD DE LEBU</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Bío-Bío</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>TECNOLOGIA BS SPA</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>76.852.815-2</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="n">
-        <v>15079.44</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>3731-192-CM26</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>2239-11-LR24</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>jul-2026</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>69.090.300-8</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>I MUNICIPALIDAD DE CHIMBARONGO</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>NETSUS SPA</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>76.288.338-4</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="n">
         <v>6886.53</v>
       </c>
     </row>
